--- a/.schema/T00_KOUTEI.xlsx
+++ b/.schema/T00_KOUTEI.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D52DF98D-4A43-4794-91F1-0C64D3C6FD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251258F2-ACDB-44BE-9CB2-070D211443DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9D3E1CD5-F2B9-4797-93E9-C328665C1881}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9D3E1CD5-F2B9-4797-93E9-C328665C1881}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.T00_KOUTEI" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.T00_KOUTEI!$A$2:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.T00_KOUTEI!$A$2:$J$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.T00_KOUTEI!$2:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,14 +38,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="32">
   <si>
     <t xml:space="preserve">8         </t>
   </si>
   <si>
-    <t>« NULL »</t>
-  </si>
-  <si>
     <t>工程７</t>
   </si>
   <si>
@@ -94,7 +91,53 @@
     <t>KOUTEI_ID</t>
   </si>
   <si>
-    <t>oracle/XEPDB1：emarf : 2026/06/24 10:26:33</t>
+    <t>A01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>A02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>A03</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>SAGYOKU_CD</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>工程８</t>
+  </si>
+  <si>
+    <t>工程９</t>
+  </si>
+  <si>
+    <t>工程１０</t>
+  </si>
+  <si>
+    <t>工程１１</t>
+  </si>
+  <si>
+    <t>工程１２</t>
+  </si>
+  <si>
+    <t>工程１３</t>
+  </si>
+  <si>
+    <t>工程１４</t>
   </si>
 </sst>
 </file>
@@ -136,7 +179,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -190,7 +232,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -212,8 +254,11 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="180"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -530,40 +575,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12441428-FDF3-4B62-B462-74268129D79A}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A2:J16"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="1"/>
+    <col min="5" max="6" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" s="8" customFormat="1" ht="86.4" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>12</v>
@@ -577,13 +616,16 @@
       <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="6">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5">
         <v>46174</v>
@@ -591,28 +633,34 @@
       <c r="D3" s="5">
         <v>46174</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="6">
+        <f>A7</f>
         <v>5</v>
       </c>
-      <c r="F3" s="3">
-        <v>46196.519118842596</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46196.519702928243</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G3" s="3" t="str">
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f t="shared" ref="I3:I16" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="6">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5">
         <v>46171</v>
@@ -620,28 +668,34 @@
       <c r="D4" s="5">
         <v>46171</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="6">
+        <f>A7</f>
         <v>5</v>
       </c>
-      <c r="F4" s="3">
-        <v>46196.51931614583</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46197.434196226852</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G16" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="6">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5">
         <v>46174</v>
@@ -649,28 +703,34 @@
       <c r="D5" s="5">
         <v>46174</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="6">
+        <f>A8</f>
         <v>6</v>
       </c>
-      <c r="F5" s="3">
-        <v>46196.51950642361</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46196.51950642361</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G5" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="6">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="5">
         <v>46171</v>
@@ -678,28 +738,34 @@
       <c r="D6" s="5">
         <v>46171</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="6">
+        <f>A8</f>
         <v>6</v>
       </c>
-      <c r="F6" s="3">
-        <v>46196.53997150463</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46197.433966898148</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G6" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="6">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="5">
         <v>46175</v>
@@ -707,28 +773,34 @@
       <c r="D7" s="5">
         <v>46175</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="6">
+        <f>A9</f>
         <v>7</v>
       </c>
-      <c r="F7" s="3">
-        <v>46196.540370219911</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46196.540489155093</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G7" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="6">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="5">
         <v>46176</v>
@@ -736,28 +808,34 @@
       <c r="D8" s="5">
         <v>46176</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6">
+        <f>A9</f>
         <v>7</v>
       </c>
-      <c r="F8" s="3">
-        <v>46196.540370219911</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46197.434529062499</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G8" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="6">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="5">
         <v>46177</v>
@@ -765,24 +843,269 @@
       <c r="D9" s="5">
         <v>46177</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3">
-        <v>46196.540370219911</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46197.4343725</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="E9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5">
+        <v>46174</v>
+      </c>
+      <c r="D10" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="6">
+        <f>A14</f>
+        <v>12</v>
+      </c>
+      <c r="G10" s="3" t="str">
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="5">
+        <v>46171</v>
+      </c>
+      <c r="D11" s="5">
+        <v>46171</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="6">
+        <f>A14</f>
+        <v>12</v>
+      </c>
+      <c r="G11" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46174</v>
+      </c>
+      <c r="D12" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="6">
+        <f>A15</f>
+        <v>13</v>
+      </c>
+      <c r="G12" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="5">
+        <v>46171</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46171</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="6">
+        <f>A15</f>
+        <v>13</v>
+      </c>
+      <c r="G13" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46175</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46175</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="6">
+        <f>A16</f>
+        <v>14</v>
+      </c>
+      <c r="G14" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="5">
+        <v>46176</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46176</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="6">
+        <f>A16</f>
+        <v>14</v>
+      </c>
+      <c r="G15" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46177</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46177</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="3" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/15 10:21:14</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I9" xr:uid="{B6E87C38-7E0A-4776-B33B-6E5095FE9942}"/>
+  <autoFilter ref="A2:J9" xr:uid="{B6E87C38-7E0A-4776-B33B-6E5095FE9942}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/.schema/T00_KOUTEI.xlsx
+++ b/.schema/T00_KOUTEI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251258F2-ACDB-44BE-9CB2-070D211443DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3780F3DE-9D13-4A62-8859-C9B4DC080277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9D3E1CD5-F2B9-4797-93E9-C328665C1881}"/>
+    <workbookView xWindow="-13965" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{9D3E1CD5-F2B9-4797-93E9-C328665C1881}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.T00_KOUTEI" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" textRotation="180"/>
     </xf>
   </cellXfs>
@@ -279,9 +279,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -319,7 +319,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -425,7 +425,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -567,7 +567,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -642,14 +642,14 @@
       </c>
       <c r="G3" s="3" t="str">
         <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="str">
         <f t="shared" ref="I3:I16" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>0</v>
@@ -677,14 +677,14 @@
       </c>
       <c r="G4" s="3" t="str">
         <f t="shared" ref="G4:G16" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>0</v>
@@ -712,14 +712,14 @@
       </c>
       <c r="G5" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I5" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>0</v>
@@ -747,14 +747,14 @@
       </c>
       <c r="G6" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>0</v>
@@ -782,14 +782,14 @@
       </c>
       <c r="G7" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>0</v>
@@ -817,14 +817,14 @@
       </c>
       <c r="G8" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>0</v>
@@ -849,14 +849,14 @@
       <c r="F9" s="4"/>
       <c r="G9" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I9" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>0</v>
@@ -884,14 +884,14 @@
       </c>
       <c r="G10" s="3" t="str">
         <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>0</v>
@@ -919,14 +919,14 @@
       </c>
       <c r="G11" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>0</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="G12" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>0</v>
@@ -989,14 +989,14 @@
       </c>
       <c r="G13" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>0</v>
@@ -1024,14 +1024,14 @@
       </c>
       <c r="G14" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>0</v>
@@ -1059,14 +1059,14 @@
       </c>
       <c r="G15" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>0</v>
@@ -1091,14 +1091,14 @@
       <c r="F16" s="4"/>
       <c r="G16" s="3" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/15 10:21:14</v>
+        <v>2026/07/24 20:10:55</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>0</v>
